--- a/data/trans_camb/IP1004-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1004-Edad-trans_camb.xlsx
@@ -792,27 +792,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,58</t>
+          <t>-1,25; 0,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,0</t>
+          <t>-2,03; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,36</t>
+          <t>-0,53; 0,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,66</t>
+          <t>-0,49; 0,57</t>
         </is>
       </c>
     </row>
@@ -943,17 +943,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 1,04</t>
+          <t>-1,79; 1,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 0,0</t>
+          <t>-3,24; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,67</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,01</t>
+          <t>-0,66; 1,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,0</t>
+          <t>-1,65; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,0</t>
+          <t>-1,43; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,0</t>
+          <t>-1,78; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 1,02</t>
+          <t>-1,85; 0,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,73; -0,29</t>
+          <t>-2,55; -0,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,46</t>
+          <t>-1,29; 0,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; -0,17</t>
+          <t>-1,5; -0,17</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,33</t>
+          <t>-0,51; 0,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,38</t>
+          <t>-0,42; 0,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,36</t>
+          <t>-0,62; 0,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; -0,17</t>
+          <t>-1,02; -0,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,24</t>
+          <t>-0,46; 0,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,0</t>
+          <t>-0,61; -0,0</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 368,78</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-87,83; 178,42</t>
+          <t>-87,33; 175,47</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 68,45</t>
+          <t>-100,0; 73,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1004-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1004-Edad-trans_camb.xlsx
@@ -792,27 +792,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,57</t>
+          <t>-1,13; 0,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,0</t>
+          <t>-1,75; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,4</t>
+          <t>-0,54; 0,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,57</t>
+          <t>-0,41; 0,7</t>
         </is>
       </c>
     </row>
@@ -943,17 +943,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,02</t>
+          <t>-1,76; 1,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 0,0</t>
+          <t>-2,89; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,01</t>
+          <t>-0,57; 1,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,0</t>
+          <t>-1,36; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,0</t>
+          <t>-1,76; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,0</t>
+          <t>-1,76; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,98</t>
+          <t>-1,84; 0,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,55; -0,29</t>
+          <t>-2,53; -0,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,39</t>
+          <t>-1,3; 0,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; -0,17</t>
+          <t>-1,77; -0,17</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,23</t>
+          <t>-0,52; 0,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,39</t>
+          <t>-0,42; 0,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,46</t>
+          <t>-0,64; 0,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,02; -0,17</t>
+          <t>-1,0; -0,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,19</t>
+          <t>-0,42; 0,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,61; -0,0</t>
+          <t>-0,57; -0,0</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 368,78</t>
+          <t>-100,0; 352,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-87,33; 175,47</t>
+          <t>-85,69; 230,9</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 73,73</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1004-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1004-Edad-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,24</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,52</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,65</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,24</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,52</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,08; 0,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,23</t>
+          <t>-1,86; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,0</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,44</t>
+          <t>-0,54; 0,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,7</t>
+          <t>-0,46; 0,66</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-46,51%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-46,51%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,49</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-0,06</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-0,57</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,49</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,03</t>
+          <t>0,0; 2,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,89</t>
+          <t>-1,75; 1,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,21; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,01</t>
+          <t>-0,58; 1,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,0</t>
+          <t>-1,1; 0,0</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-11,04%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,46</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,94</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,35</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,35</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,46</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,94</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>-1,72; 1,02</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>-2,73; -0,29</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>-1,99; 0,0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>-1,76; 0,0</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-1,76; 0,0</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-1,84; 0,97</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-2,53; -0,29</t>
-        </is>
-      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,34</t>
+          <t>-1,2; 0,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,77; -0,17</t>
+          <t>-1,62; -0,17</t>
         </is>
       </c>
     </row>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-48,65%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-48,65%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,13</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,45</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-0,1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-0,01</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,23</t>
+          <t>-0,67; 0,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,37</t>
+          <t>-1,0; -0,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,41</t>
+          <t>-0,42; 0,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; -0,17</t>
+          <t>-0,42; 0,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,24</t>
+          <t>-0,43; 0,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; -0,0</t>
+          <t>-0,54; 0,0</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-29,4%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-46,2%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-7,07%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-29,4%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 352,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-85,69; 230,9</t>
+          <t>-87,83; 178,42</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 68,45</t>
         </is>
       </c>
     </row>
